--- a/public/formsExcelTemplates/Solicitud de laboratorio clínico.xlsx
+++ b/public/formsExcelTemplates/Solicitud de laboratorio clínico.xlsx
@@ -81,7 +81,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -204,12 +204,55 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -219,52 +262,22 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
@@ -312,7 +325,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -350,13 +363,16 @@
     <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -938,24 +954,24 @@
     </row>
     <row r="6">
       <c r="A6" s="7"/>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="9"/>
     </row>
     <row r="7" ht="15">
       <c r="A7" s="10"/>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="3">
